--- a/Assets/Data/Excel/PropData.xlsx
+++ b/Assets/Data/Excel/PropData.xlsx
@@ -1,138 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF85831-C525-4FD2-8F23-48BDF62AD9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34110" yWindow="4290" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-6630" yWindow="4020" windowWidth="13395" windowHeight="15540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>grade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prop_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级是1 普通、2 稀有、3 史诗 、4 传说</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具的id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图标的资源地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具类型 ，暂时无意义，为了可能的未来</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_Ids</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具包含的属性ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prop_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是道具的具体属性值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是道具的基础金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -151,24 +53,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,107 +395,567 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="24.25" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="2" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
-    <col min="5" max="5" width="13.625" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
+    <col width="9.625" customWidth="1" min="1" max="1"/>
+    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="10.75" customWidth="1" min="3" max="3"/>
+    <col width="14.375" customWidth="1" min="4" max="4"/>
+    <col width="15.875" customWidth="1" min="6" max="6"/>
+    <col width="19.875" customWidth="1" min="7" max="7"/>
+    <col width="18.25" customWidth="1" min="8" max="8"/>
+    <col width="19.875" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="15.875" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>prop_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>attr_Ids</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_data</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>coin</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>exclude_ids</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>is_unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float[]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string[]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>品阶</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>属性ID组</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>数值组</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>流派</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>互斥ID</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>是否唯一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>急速皮靴</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Icon/SpeedBoots</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>生锈铁剑</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Icon/RustySword</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>狂暴指环</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Icon/PowerRing</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>精良长弓</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Icon/GoodBow</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>稳重护符</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Icon/GuardAmulet</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>150</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>107</v>
+      </c>
+      <c r="B9" t="n">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>战神铠甲</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Icon/WarArmor</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>激光枪</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Icon/LaserGun</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>600</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104</v>
+      </c>
+      <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>唯一圣剑</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Icon/HolySword</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/PropData.xlsx
+++ b/Assets/Data/Excel/PropData.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-6630" yWindow="4020" windowWidth="13395" windowHeight="15540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -400,7 +400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="24.25" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="9.625" customWidth="1" min="1" max="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>急速皮靴</t>
+          <t>炸药饭</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Icon/SpeedBoots</t>
+          <t>Icon/fried_rice_icon</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -608,23 +608,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Explosion</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -633,43 +632,42 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>生锈铁剑</t>
+          <t>导弹来袭</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Icon/RustySword</t>
+          <t>Icon/missile_icon</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Explosion|Projectile</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -678,19 +676,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>狂暴指环</t>
+          <t>合金</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Icon/PowerRing</t>
+          <t>Icon/alloy_icon</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -698,25 +696,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>103</t>
+          <t>Melee</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -727,43 +720,42 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>精良长弓</t>
+          <t>水蛭</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Icon/GoodBow</t>
+          <t>Icon/blood_leech_icon</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Melee|Sustain</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -772,19 +764,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>稳重护符</t>
+          <t>铁砧</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Icon/GuardAmulet</t>
+          <t>Icon/anvil_icon</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -792,25 +784,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>102</t>
+          <t>Melee|AttackSpeed</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -821,19 +808,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>战神铠甲</t>
+          <t>舔食者</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Icon/WarArmor</t>
+          <t>Icon/alien_tongue_icon</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -841,23 +828,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Projectile</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -866,43 +852,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>激光枪</t>
+          <t>散射眼球</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Icon/LaserGun</t>
+          <t>Icon/alien_eyes_icon</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23,1,3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1,-10,-1</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Projectile</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -911,49 +896,100 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>唯一圣剑</t>
+          <t>激素大脑</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Icon/HolySword</t>
+          <t>Icon/adrenaline_icon</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10,3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Projectile|AttackSpeed</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>109</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>小血瓶</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Icon/potion_icon</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sustain</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
